--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251002_172408.xlsx
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
